--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488174_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488174_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7279</v>
+        <v>6.1755</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7093</v>
+        <v>4.9599</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0186</v>
+        <v>1.2156</v>
       </c>
       <c r="G2" t="n">
         <v>6.7787</v>
@@ -610,13 +610,13 @@
         <v>0.9264</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7083</v>
+        <v>1.1559</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1816</v>
+        <v>0.4321</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5266999999999999</v>
+        <v>0.7237</v>
       </c>
       <c r="V2" t="n">
         <v>-1.5738</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5998</v>
+        <v>6.0008</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9015</v>
+        <v>2.6964</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6983</v>
+        <v>3.3044</v>
       </c>
       <c r="G3" t="n">
         <v>2.3874</v>
@@ -688,13 +688,13 @@
         <v>1.6676</v>
       </c>
       <c r="S3" t="n">
-        <v>1.88</v>
+        <v>2.2809</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2997</v>
+        <v>1.0946</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5802</v>
+        <v>1.1863</v>
       </c>
       <c r="V3" t="n">
         <v>1.8883</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.895</v>
+        <v>3.7383</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2168</v>
+        <v>3.006</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6782</v>
+        <v>0.7323</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3644</v>
+        <v>3.3416</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5026</v>
+        <v>3.4598</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8619</v>
+        <v>-0.1183</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6744</v>
+        <v>2.6391</v>
       </c>
       <c r="K4" t="n">
-        <v>1.55</v>
+        <v>3.7789</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1244</v>
+        <v>-1.1398</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.31</v>
+        <v>0.7025</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0474</v>
+        <v>-0.3191</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7374000000000001</v>
+        <v>1.0216</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0382</v>
+        <v>-0.1853</v>
       </c>
       <c r="R4" t="n">
-        <v>1.297</v>
+        <v>0.3706</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0685</v>
+        <v>0.2114</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3779</v>
+        <v>0.5521</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6906</v>
+        <v>-0.3407</v>
       </c>
       <c r="V4" t="n">
-        <v>2.2033</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2027</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0014</v>
+        <v>3.4041</v>
       </c>
       <c r="E5" t="n">
-        <v>3.343</v>
+        <v>2.2922</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6584</v>
+        <v>1.1119</v>
       </c>
       <c r="G5" t="n">
-        <v>3.3416</v>
+        <v>1.3644</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4598</v>
+        <v>0.5026</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1183</v>
+        <v>0.8619</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6391</v>
+        <v>1.6744</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7789</v>
+        <v>1.55</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1398</v>
+        <v>0.1244</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7025</v>
+        <v>-0.31</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3191</v>
+        <v>-1.0474</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0216</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1853</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1853</v>
+        <v>-2.0382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3706</v>
+        <v>1.297</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4745</v>
+        <v>0.5776</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8891</v>
+        <v>0.4533</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4146</v>
+        <v>0.1243</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.2033</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.2027</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9121</v>
+        <v>2.8448</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6297</v>
+        <v>2.4885</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2824</v>
+        <v>0.3563</v>
       </c>
       <c r="G6" t="n">
         <v>1.563</v>
@@ -922,13 +922,13 @@
         <v>0.7411</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4221</v>
+        <v>1.3548</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0409</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3812</v>
+        <v>0.4551</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6289</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.171</v>
+        <v>1.6376</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4895</v>
+        <v>1.0545</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6815</v>
+        <v>0.583</v>
       </c>
       <c r="G8" t="n">
         <v>2.3152</v>
@@ -1078,13 +1078,13 @@
         <v>0.7411</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7996</v>
+        <v>1.2662</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2933</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5063</v>
+        <v>0.4079</v>
       </c>
       <c r="V8" t="n">
         <v>-1.5733</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PINILLA NUNEZ</t>
+          <t>J. RIBEIROS CARREIRAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6811</v>
+        <v>1.5679</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2774</v>
+        <v>-0.9555</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4037</v>
+        <v>2.5234</v>
       </c>
       <c r="G9" t="n">
-        <v>0.796</v>
+        <v>3.7857</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4595</v>
+        <v>-0.3783</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6635</v>
+        <v>4.164</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6939</v>
+        <v>3.074</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1809</v>
+        <v>-0.2449</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.487</v>
+        <v>3.319</v>
       </c>
       <c r="M9" t="n">
-        <v>0.102</v>
+        <v>0.7116</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2786</v>
+        <v>-0.1334</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1766</v>
+        <v>0.845</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-3.1499</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.297</v>
+        <v>-4.6322</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7411</v>
+        <v>1.4823</v>
       </c>
       <c r="S9" t="n">
-        <v>0.441</v>
+        <v>0.6177</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8804</v>
+        <v>0.2882</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4395</v>
+        <v>0.3295</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RIBEIROS CARREIRAS</t>
+          <t>J. PINILLA NUNEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4841</v>
+        <v>1.1538</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8916</v>
+        <v>0.43</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3757</v>
+        <v>0.7238</v>
       </c>
       <c r="G10" t="n">
-        <v>3.7857</v>
+        <v>0.796</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3783</v>
+        <v>1.4595</v>
       </c>
       <c r="I10" t="n">
-        <v>4.164</v>
+        <v>-0.6635</v>
       </c>
       <c r="J10" t="n">
-        <v>3.074</v>
+        <v>0.6939</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2449</v>
+        <v>1.1809</v>
       </c>
       <c r="L10" t="n">
-        <v>3.319</v>
+        <v>-0.487</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7116</v>
+        <v>0.102</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1334</v>
+        <v>0.2786</v>
       </c>
       <c r="O10" t="n">
-        <v>0.845</v>
+        <v>-0.1766</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.1499</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.6322</v>
+        <v>-1.297</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4823</v>
+        <v>0.7411</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4661</v>
+        <v>0.9137</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6479</v>
+        <v>1.0331</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1818</v>
+        <v>-0.1194</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3755</v>
+        <v>0.3022</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4208</v>
+        <v>-0.5187</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7963</v>
+        <v>0.8209</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4819</v>
@@ -1312,13 +1312,13 @@
         <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9304</v>
+        <v>0.8571</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6404</v>
+        <v>0.5425</v>
       </c>
       <c r="U11" t="n">
-        <v>0.29</v>
+        <v>0.3146</v>
       </c>
       <c r="V11" t="n">
         <v>0.0005</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8599</v>
+        <v>-1.6881</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5578</v>
+        <v>-1.4599</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.302</v>
+        <v>-0.2282</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8208</v>
@@ -1390,13 +1390,13 @@
         <v>0.1853</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2243</v>
+        <v>-0.0525</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2736</v>
+        <v>-0.1756</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0492</v>
+        <v>0.1231</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9712</v>
+        <v>-1.9465</v>
       </c>
       <c r="E13" t="n">
         <v>-1.6887</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2824</v>
+        <v>-0.2578</v>
       </c>
       <c r="G13" t="n">
         <v>-0.9517</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.093</v>
+        <v>-0.0684</v>
       </c>
       <c r="T13" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.0068</v>
+        <v>-3.6331</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.1799</v>
+        <v>-1.9293</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8269</v>
+        <v>-1.7038</v>
       </c>
       <c r="G14" t="n">
         <v>-1.2571</v>
@@ -1546,13 +1546,13 @@
         <v>0.1853</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2674</v>
+        <v>0.1063</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2189</v>
+        <v>0.0317</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0485</v>
+        <v>0.0746</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6294</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>21.8424</v>
+        <v>22.3897</v>
       </c>
       <c r="E15" t="n">
-        <v>12.6608</v>
+        <v>13.2078</v>
       </c>
       <c r="F15" t="n">
         <v>9.181800000000001</v>
@@ -1591,7 +1591,7 @@
         <v>19.6529</v>
       </c>
       <c r="H15" t="n">
-        <v>7.979200000000001</v>
+        <v>7.9792</v>
       </c>
       <c r="I15" t="n">
         <v>11.6736</v>
@@ -1603,7 +1603,7 @@
         <v>11.4026</v>
       </c>
       <c r="L15" t="n">
-        <v>7.563400000000001</v>
+        <v>7.563399999999999</v>
       </c>
       <c r="M15" t="n">
         <v>0.6865999999999997</v>
@@ -1612,10 +1612,10 @@
         <v>-3.4233</v>
       </c>
       <c r="O15" t="n">
-        <v>4.11</v>
+        <v>4.110000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-6.4851</v>
+        <v>-6.485100000000001</v>
       </c>
       <c r="Q15" t="n">
         <v>-15.7494</v>
@@ -1624,13 +1624,13 @@
         <v>9.264199999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>8.6736</v>
+        <v>9.220699999999997</v>
       </c>
       <c r="T15" t="n">
-        <v>5.353499999999999</v>
+        <v>5.9007</v>
       </c>
       <c r="U15" t="n">
-        <v>3.319799999999999</v>
+        <v>3.319999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>0.001100000000000323</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7312</v>
+        <v>2.3641</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3714</v>
+        <v>1.9797</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3599</v>
+        <v>0.3845</v>
       </c>
       <c r="G16" t="n">
         <v>1.8008</v>
@@ -1702,13 +1702,13 @@
         <v>0.7411</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1893</v>
+        <v>-0.1778</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3793</v>
+        <v>-0.0124</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.19</v>
+        <v>-0.1654</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5992</v>
+        <v>0.4214</v>
       </c>
       <c r="E18" t="n">
-        <v>0.679</v>
+        <v>1.3645</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2781</v>
+        <v>-0.9431</v>
       </c>
       <c r="G18" t="n">
         <v>-0.3367</v>
@@ -1858,13 +1858,13 @@
         <v>1.6676</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3361</v>
+        <v>-0.3155</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9426</v>
+        <v>-0.2571</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3935</v>
+        <v>-0.0585</v>
       </c>
       <c r="V18" t="n">
         <v>1.2589</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1902</v>
+        <v>-0.6834</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9945000000000001</v>
+        <v>1.0924</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1848</v>
+        <v>-1.7759</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1834</v>
@@ -1936,13 +1936,13 @@
         <v>1.4823</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.1921</v>
+        <v>-1.6853</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0396</v>
+        <v>-0.9417</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1525</v>
+        <v>-0.7436</v>
       </c>
       <c r="V19" t="n">
         <v>0.6294</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. MARKWARDT FERNANDES</t>
+          <t>S. VALIENTE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4096</v>
+        <v>-1.176</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1274</v>
+        <v>-0.9008</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2822</v>
+        <v>-0.2752</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5393</v>
+        <v>-0.636</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0105</v>
+        <v>-1.5669</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5498</v>
+        <v>0.9308</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1274</v>
+        <v>0.4748</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0859</v>
+        <v>-0.8937</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0415</v>
+        <v>1.3686</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6667</v>
+        <v>-1.1108</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.6731</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5913</v>
+        <v>-0.4377</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3706</v>
+        <v>0.1853</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.1117</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4997</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3283</v>
+        <v>-0.4492</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1714</v>
+        <v>-0.2761</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. VALIENTE RODRIGUEZ</t>
+          <t>R. MARKWARDT FERNANDES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4859</v>
+        <v>-1.2469</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9988</v>
+        <v>-1.1274</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4871</v>
+        <v>-0.1195</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.636</v>
+        <v>-0.5393</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5669</v>
+        <v>0.0105</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9308</v>
+        <v>-0.5498</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4748</v>
+        <v>0.1274</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8937</v>
+        <v>0.0859</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3686</v>
+        <v>0.0415</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1108</v>
+        <v>-0.6667</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6731</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4377</v>
+        <v>-0.5913</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1853</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0351</v>
+        <v>-0.337</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5471</v>
+        <v>-0.3283</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.488</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. TRAORE</t>
+          <t>R. RUBIO SANCHEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7544</v>
+        <v>-1.7985</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3036</v>
+        <v>-2.6831</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4508</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5344</v>
+        <v>-1.0785</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1291</v>
+        <v>-0.8589</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4053</v>
+        <v>-0.2197</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1539</v>
+        <v>-1.2643</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0295</v>
+        <v>-0.6529</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1244</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6884</v>
+        <v>0.1857</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.1587</v>
+        <v>-0.206</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5296999999999999</v>
+        <v>0.3917</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>2.7793</v>
+        <v>0.9264</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5004</v>
+        <v>-0.72</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4689</v>
+        <v>-0.4924</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0315</v>
+        <v>-0.2276</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. RUBIO SANCHEZ</t>
+          <t>A. CHAPARRO CARRASCO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.897</v>
+        <v>-2.6044</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6831</v>
+        <v>-1.3754</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7861</v>
+        <v>-1.2289</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.0785</v>
+        <v>-2.9019</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8589</v>
+        <v>0.9812</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2197</v>
+        <v>-3.8831</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2643</v>
+        <v>-1.0636</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6529</v>
+        <v>2.1592</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-3.2228</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1857</v>
+        <v>-1.8382</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.206</v>
+        <v>-1.178</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3917</v>
+        <v>-0.6603</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.8529</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9264</v>
+        <v>1.8529</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8185</v>
+        <v>-0.6115</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4924</v>
+        <v>-0.3118</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3261</v>
+        <v>-0.2997</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. BARRIENTOS PRIETO</t>
+          <t>I. TRAORE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3134</v>
+        <v>-2.622</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1395</v>
+        <v>-0.9891</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1739</v>
+        <v>-1.6329</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.9538</v>
+        <v>-2.5344</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.5314</v>
+        <v>-2.1291</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4223</v>
+        <v>-0.4053</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8112</v>
+        <v>0.1539</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2413</v>
+        <v>0.0295</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5699</v>
+        <v>0.1244</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1426</v>
+        <v>-2.6884</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2901</v>
+        <v>-2.1587</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8524</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.8529</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5558999999999999</v>
+        <v>2.7793</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9155</v>
+        <v>-0.3671</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3283</v>
+        <v>-0.2167</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.1505</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. CHAPARRO CARRASCO</t>
+          <t>J. BARRIENTOS PRIETO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.551</v>
+        <v>-2.9538</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.0609</v>
+        <v>-2.1395</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4901</v>
+        <v>-0.8143</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.9019</v>
+        <v>-2.9538</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9812</v>
+        <v>-1.5314</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.8831</v>
+        <v>-1.4223</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.0636</v>
+        <v>-1.8112</v>
       </c>
       <c r="K25" t="n">
-        <v>2.1592</v>
+        <v>-1.2413</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.2228</v>
+        <v>-0.5699</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.8382</v>
+        <v>-1.1426</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.178</v>
+        <v>-0.2901</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.6603</v>
+        <v>-0.8524</v>
       </c>
       <c r="P25" t="n">
-        <v>1.8529</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8529</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5582</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9973</v>
+        <v>-0.3283</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5609</v>
+        <v>-0.2276</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.104</v>
+        <v>-4.3555</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.8225</v>
+        <v>-2.6059</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.2815</v>
+        <v>-1.7496</v>
       </c>
       <c r="G26" t="n">
         <v>-4.5654</v>
@@ -2482,13 +2482,13 @@
         <v>1.1117</v>
       </c>
       <c r="S26" t="n">
-        <v>0.9056</v>
+        <v>0.6541</v>
       </c>
       <c r="T26" t="n">
-        <v>1.4537</v>
+        <v>0.6703</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5482</v>
+        <v>-0.0162</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6294</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.9131</v>
+        <v>-5.2202</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.735</v>
+        <v>-2.4412</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.1781</v>
+        <v>-2.779</v>
       </c>
       <c r="G27" t="n">
         <v>-6.3683</v>
@@ -2560,13 +2560,13 @@
         <v>2.9646</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.9138</v>
+        <v>-1.2208</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9463</v>
+        <v>-0.6525</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.9675</v>
+        <v>-0.5683</v>
       </c>
       <c r="V27" t="n">
         <v>1.2572</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-21.8425</v>
+        <v>-19.2311</v>
       </c>
       <c r="E28" t="n">
-        <v>-9.181799999999999</v>
+        <v>-9.181700000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-12.6606</v>
+        <v>-10.0493</v>
       </c>
       <c r="G28" t="n">
         <v>-19.6528</v>
@@ -2611,7 +2611,7 @@
         <v>-11.6737</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6867999999999999</v>
+        <v>-0.6867999999999994</v>
       </c>
       <c r="K28" t="n">
         <v>3.4233</v>
@@ -2632,19 +2632,19 @@
         <v>6.4851</v>
       </c>
       <c r="Q28" t="n">
-        <v>-9.264199999999999</v>
+        <v>-9.264200000000001</v>
       </c>
       <c r="R28" t="n">
         <v>15.7494</v>
       </c>
       <c r="S28" t="n">
-        <v>-8.6737</v>
+        <v>-6.062100000000001</v>
       </c>
       <c r="T28" t="n">
-        <v>-3.32</v>
+        <v>-3.3201</v>
       </c>
       <c r="U28" t="n">
-        <v>-5.353800000000001</v>
+        <v>-2.7422</v>
       </c>
       <c r="V28" t="n">
         <v>-0.001099999999999879</v>
